--- a/exports/trend_1d/PERSISTENT_full_report.xlsx
+++ b/exports/trend_1d/PERSISTENT_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:U72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>15.61</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42072</v>
+        <v>42073</v>
       </c>
       <c r="H2" t="n">
-        <v>466.35</v>
+        <v>424.5</v>
       </c>
       <c r="I2" t="n">
         <v>434.0102493583149</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K2" t="n">
-        <v>4.49</v>
+        <v>-4.88</v>
       </c>
       <c r="L2" t="n">
         <v>9.83</v>
       </c>
       <c r="M2" t="n">
-        <v>0.46</v>
+        <v>2.96</v>
       </c>
       <c r="N2" t="n">
-        <v>5.36</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="O2" t="n">
         <v>-0.1</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>14.39</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42138</v>
+        <v>42139</v>
       </c>
       <c r="H3" t="n">
-        <v>362.8</v>
+        <v>387.6</v>
       </c>
       <c r="I3" t="n">
         <v>374.4628703295579</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K3" t="n">
-        <v>14.53</v>
+        <v>8.69</v>
       </c>
       <c r="L3" t="n">
         <v>7.77</v>
@@ -612,7 +647,7 @@
         <v>2.76</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>6.84</v>
       </c>
       <c r="O3" t="n">
         <v>-8.970000000000001</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>13.84</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42173</v>
+        <v>42174</v>
       </c>
       <c r="H4" t="n">
-        <v>360.2</v>
+        <v>356.8</v>
       </c>
       <c r="I4" t="n">
         <v>357.5195872975967</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.07</v>
+        <v>-7.95</v>
       </c>
       <c r="L4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="M4" t="n">
         <v>1.47</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>10.72</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42221</v>
+        <v>42222</v>
       </c>
       <c r="H5" t="n">
-        <v>339.2</v>
+        <v>347</v>
       </c>
       <c r="I5" t="n">
         <v>339.6032631838459</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K5" t="n">
-        <v>4.93</v>
+        <v>2.75</v>
       </c>
       <c r="L5" t="n">
         <v>2.72</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>10.52</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H6" t="n">
-        <v>350.6</v>
+        <v>337.4</v>
       </c>
       <c r="I6" t="n">
         <v>345.5215897349001</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>1.04</v>
+        <v>-2.77</v>
       </c>
       <c r="L6" t="n">
-        <v>2.31</v>
+        <v>6.34</v>
       </c>
       <c r="M6" t="n">
-        <v>1.24</v>
+        <v>6.59</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="O6" t="n">
         <v>2.3</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.38</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42397</v>
+        <v>42398</v>
       </c>
       <c r="H7" t="n">
-        <v>319.4</v>
+        <v>331.45</v>
       </c>
       <c r="I7" t="n">
         <v>326.0453353492813</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K7" t="n">
-        <v>5.33</v>
+        <v>1.76</v>
       </c>
       <c r="L7" t="n">
         <v>6.7</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>7</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>12.2</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42410</v>
+        <v>42411</v>
       </c>
       <c r="H8" t="n">
-        <v>305.9</v>
+        <v>299.9</v>
       </c>
       <c r="I8" t="n">
         <v>300.9992442451805</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K8" t="n">
-        <v>-7.71</v>
+        <v>-9.52</v>
       </c>
       <c r="L8" t="n">
-        <v>7.97</v>
+        <v>11.6</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>12.45</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42446</v>
+        <v>42447</v>
       </c>
       <c r="H9" t="n">
-        <v>327.1</v>
+        <v>336.1</v>
       </c>
       <c r="I9" t="n">
         <v>331.3853174243622</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.07</v>
+        <v>-12.07</v>
       </c>
       <c r="L9" t="n">
         <v>14.04</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>12.61</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42537</v>
+        <v>42538</v>
       </c>
       <c r="H10" t="n">
-        <v>352.4</v>
+        <v>342.7</v>
       </c>
       <c r="I10" t="n">
         <v>347.8517135215754</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K10" t="n">
-        <v>4.85</v>
+        <v>1.96</v>
       </c>
       <c r="L10" t="n">
         <v>3.3</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.88</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42576</v>
+        <v>42577</v>
       </c>
       <c r="H11" t="n">
-        <v>332.7</v>
+        <v>345.6</v>
       </c>
       <c r="I11" t="n">
         <v>343.4601626172324</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K11" t="n">
-        <v>2.92</v>
+        <v>-0.85</v>
       </c>
       <c r="L11" t="n">
         <v>5.02</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>10.75</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42607</v>
+        <v>42608</v>
       </c>
       <c r="H12" t="n">
-        <v>320.2</v>
+        <v>315.5</v>
       </c>
       <c r="I12" t="n">
         <v>316.6302235761505</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K12" t="n">
-        <v>-7.35</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>8.33</v>
+        <v>9.51</v>
       </c>
       <c r="M12" t="n">
         <v>0.75</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42646</v>
+        <v>42647</v>
       </c>
       <c r="H13" t="n">
-        <v>320.1</v>
+        <v>330.7</v>
       </c>
       <c r="I13" t="n">
         <v>320.6069467156807</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.46</v>
+        <v>-4.82</v>
       </c>
       <c r="L13" t="n">
-        <v>2.49</v>
+        <v>6.02</v>
       </c>
       <c r="M13" t="n">
         <v>2.31</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>9.69</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42685</v>
+        <v>42689</v>
       </c>
       <c r="H14" t="n">
-        <v>320</v>
+        <v>306.7</v>
       </c>
       <c r="I14" t="n">
         <v>315.6602180428068</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.24</v>
+        <v>-7.26</v>
       </c>
       <c r="L14" t="n">
-        <v>5.5</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>3.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.44</v>
+        <v>4.16</v>
       </c>
       <c r="O14" t="n">
         <v>3.31</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>12.07</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42738</v>
+        <v>42739</v>
       </c>
       <c r="H15" t="n">
-        <v>313.9</v>
+        <v>323.4</v>
       </c>
       <c r="I15" t="n">
         <v>317.6533679885014</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.35</v>
+        <v>-5.45</v>
       </c>
       <c r="L15" t="n">
-        <v>4.34</v>
+        <v>7.84</v>
       </c>
       <c r="M15" t="n">
         <v>1.77</v>
       </c>
       <c r="N15" t="n">
-        <v>2.62</v>
+        <v>3.03</v>
       </c>
       <c r="O15" t="n">
         <v>-4.16</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42766</v>
+        <v>42767</v>
       </c>
       <c r="H16" t="n">
-        <v>297.3</v>
+        <v>293</v>
       </c>
       <c r="I16" t="n">
         <v>296.7493688883815</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K16" t="n">
-        <v>-8.07</v>
+        <v>-9.4</v>
       </c>
       <c r="L16" t="n">
-        <v>8.779999999999999</v>
+        <v>10.33</v>
       </c>
       <c r="M16" t="n">
         <v>2.39</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42794</v>
+        <v>42795</v>
       </c>
       <c r="H17" t="n">
-        <v>318.2</v>
+        <v>320.2</v>
       </c>
       <c r="I17" t="n">
         <v>319.2454946053774</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K17" t="n">
-        <v>-8.6</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="L17" t="n">
         <v>10.75</v>
       </c>
       <c r="M17" t="n">
-        <v>0.87</v>
+        <v>1.3</v>
       </c>
       <c r="N17" t="n">
         <v>1.89</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>7.92</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42825</v>
+        <v>42828</v>
       </c>
       <c r="H18" t="n">
-        <v>297.85</v>
+        <v>294.2</v>
       </c>
       <c r="I18" t="n">
         <v>294.8522104482836</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.98</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>7.84</v>
+        <v>8.49</v>
       </c>
       <c r="M18" t="n">
         <v>1.16</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>8.01</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42884</v>
+        <v>42885</v>
       </c>
       <c r="H19" t="n">
-        <v>289.8</v>
+        <v>300.3</v>
       </c>
       <c r="I19" t="n">
         <v>299.6343615210214</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5</v>
+        <v>-2.07</v>
       </c>
       <c r="L19" t="n">
-        <v>2.33</v>
+        <v>2.99</v>
       </c>
       <c r="M19" t="n">
         <v>2.22</v>
       </c>
       <c r="N19" t="n">
-        <v>2.24</v>
+        <v>3.62</v>
       </c>
       <c r="O19" t="n">
         <v>-1.23</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>8.42</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42951</v>
+        <v>42954</v>
       </c>
       <c r="H20" t="n">
-        <v>318.95</v>
+        <v>310.8</v>
       </c>
       <c r="I20" t="n">
         <v>315.8116813060874</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K20" t="n">
-        <v>6.21</v>
+        <v>3.5</v>
       </c>
       <c r="L20" t="n">
         <v>5.19</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>8.69</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43003</v>
+        <v>43004</v>
       </c>
       <c r="H21" t="n">
-        <v>318.7</v>
+        <v>325.65</v>
       </c>
       <c r="I21" t="n">
         <v>324.7031349364058</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.54</v>
+        <v>-4.78</v>
       </c>
       <c r="L21" t="n">
-        <v>4.25</v>
+        <v>6.18</v>
       </c>
       <c r="M21" t="n">
         <v>1.52</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>8.25</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43186</v>
+        <v>43187</v>
       </c>
       <c r="H22" t="n">
-        <v>392.05</v>
+        <v>347</v>
       </c>
       <c r="I22" t="n">
         <v>379.9414856769431</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K22" t="n">
-        <v>20.39</v>
+        <v>6.56</v>
       </c>
       <c r="L22" t="n">
         <v>3.42</v>
       </c>
       <c r="M22" t="n">
-        <v>4.85</v>
+        <v>8.17</v>
       </c>
       <c r="N22" t="n">
-        <v>4.49</v>
+        <v>11.49</v>
       </c>
       <c r="O22" t="n">
         <v>2.18</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>19.09</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43214</v>
+        <v>43215</v>
       </c>
       <c r="H23" t="n">
-        <v>363.15</v>
+        <v>384.2</v>
       </c>
       <c r="I23" t="n">
         <v>376.126047828618</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.65</v>
+        <v>-10.72</v>
       </c>
       <c r="L23" t="n">
         <v>12.48</v>
@@ -1752,7 +2027,7 @@
         <v>1.8</v>
       </c>
       <c r="N23" t="n">
-        <v>4.89</v>
+        <v>5.8</v>
       </c>
       <c r="O23" t="n">
         <v>-11.49</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>15.19</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43368</v>
+        <v>43369</v>
       </c>
       <c r="H24" t="n">
-        <v>404.75</v>
+        <v>396.4</v>
       </c>
       <c r="I24" t="n">
         <v>400.4804340296005</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K24" t="n">
-        <v>5.35</v>
+        <v>3.18</v>
       </c>
       <c r="L24" t="n">
         <v>5.44</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>6</v>
+      </c>
+      <c r="U24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>14.18</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43431</v>
+        <v>43432</v>
       </c>
       <c r="H25" t="n">
-        <v>282.5</v>
+        <v>301.05</v>
       </c>
       <c r="I25" t="n">
         <v>300.8521131534642</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K25" t="n">
-        <v>28.73</v>
+        <v>24.05</v>
       </c>
       <c r="L25" t="n">
         <v>4.52</v>
@@ -1866,7 +2165,7 @@
         <v>2.89</v>
       </c>
       <c r="N25" t="n">
-        <v>3.43</v>
+        <v>6.57</v>
       </c>
       <c r="O25" t="n">
         <v>-2.06</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.45</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43468</v>
+        <v>43469</v>
       </c>
       <c r="H26" t="n">
-        <v>306.8</v>
+        <v>288.65</v>
       </c>
       <c r="I26" t="n">
         <v>292.1728081247504</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K26" t="n">
-        <v>1.91</v>
+        <v>-4.12</v>
       </c>
       <c r="L26" t="n">
         <v>6.16</v>
@@ -1923,7 +2234,7 @@
         <v>1.89</v>
       </c>
       <c r="N26" t="n">
-        <v>2.78</v>
+        <v>5.92</v>
       </c>
       <c r="O26" t="n">
         <v>6.57</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>13.25</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43494</v>
+        <v>43495</v>
       </c>
       <c r="H27" t="n">
-        <v>291.7</v>
+        <v>300.9</v>
       </c>
       <c r="I27" t="n">
         <v>294.6145105832992</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.06</v>
+        <v>-4.24</v>
       </c>
       <c r="L27" t="n">
         <v>7.33</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>9.57</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43566</v>
+        <v>43567</v>
       </c>
       <c r="H28" t="n">
-        <v>311.35</v>
+        <v>305.4</v>
       </c>
       <c r="I28" t="n">
         <v>306.0363533738456</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K28" t="n">
-        <v>3.47</v>
+        <v>1.5</v>
       </c>
       <c r="L28" t="n">
         <v>2.76</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>10.45</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43626</v>
+        <v>43627</v>
       </c>
       <c r="H29" t="n">
-        <v>304.6</v>
+        <v>316.75</v>
       </c>
       <c r="I29" t="n">
         <v>307.2059776499557</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K29" t="n">
-        <v>0.26</v>
+        <v>-3.72</v>
       </c>
       <c r="L29" t="n">
-        <v>5.22</v>
+        <v>5.8</v>
       </c>
       <c r="M29" t="n">
         <v>1.68</v>
       </c>
       <c r="N29" t="n">
-        <v>2.13</v>
+        <v>3.99</v>
       </c>
       <c r="O29" t="n">
         <v>-1.91</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>8.32</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43664</v>
+        <v>43665</v>
       </c>
       <c r="H30" t="n">
-        <v>304</v>
+        <v>288.6</v>
       </c>
       <c r="I30" t="n">
         <v>294.4958228959512</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.03</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>4.28</v>
+        <v>9.23</v>
       </c>
       <c r="M30" t="n">
         <v>1.59</v>
       </c>
       <c r="N30" t="n">
-        <v>2.21</v>
+        <v>5.07</v>
       </c>
       <c r="O30" t="n">
         <v>3.99</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>10.73</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43721</v>
+        <v>43724</v>
       </c>
       <c r="H31" t="n">
-        <v>286.5</v>
+        <v>291</v>
       </c>
       <c r="I31" t="n">
         <v>287.6187708083622</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K31" t="n">
-        <v>0.73</v>
+        <v>-0.83</v>
       </c>
       <c r="L31" t="n">
         <v>5.99</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43901</v>
+        <v>43902</v>
       </c>
       <c r="H32" t="n">
-        <v>343.2</v>
+        <v>323.8</v>
       </c>
       <c r="I32" t="n">
         <v>336.0036929032791</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K32" t="n">
-        <v>17.94</v>
+        <v>11.27</v>
       </c>
       <c r="L32" t="n">
         <v>6.08</v>
       </c>
       <c r="M32" t="n">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="N32" t="n">
-        <v>5.11</v>
+        <v>5.65</v>
       </c>
       <c r="O32" t="n">
         <v>1.57</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>7</v>
+      </c>
+      <c r="U32" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>12.92</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H33" t="n">
-        <v>262.8</v>
+        <v>275.7</v>
       </c>
       <c r="I33" t="n">
         <v>268.9121303442284</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K33" t="n">
-        <v>18.84</v>
+        <v>14.85</v>
       </c>
       <c r="L33" t="n">
         <v>4.39</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>12.06</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44071</v>
+        <v>44074</v>
       </c>
       <c r="H34" t="n">
-        <v>509.1</v>
+        <v>479.1</v>
       </c>
       <c r="I34" t="n">
         <v>480.4721252216038</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K34" t="n">
-        <v>84.66</v>
+        <v>73.78</v>
       </c>
       <c r="L34" t="n">
         <v>4.13</v>
@@ -2379,7 +2786,7 @@
         <v>5</v>
       </c>
       <c r="N34" t="n">
-        <v>4.75</v>
+        <v>5.89</v>
       </c>
       <c r="O34" t="n">
         <v>4.91</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>19.3</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44085</v>
+        <v>44088</v>
       </c>
       <c r="H35" t="n">
-        <v>505.5</v>
+        <v>577.05</v>
       </c>
       <c r="I35" t="n">
         <v>558.3079479949313</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.51</v>
+        <v>-20.44</v>
       </c>
       <c r="L35" t="n">
-        <v>9.91</v>
+        <v>23.98</v>
       </c>
       <c r="M35" t="n">
         <v>1.94</v>
       </c>
       <c r="N35" t="n">
-        <v>5.26</v>
+        <v>14.15</v>
       </c>
       <c r="O35" t="n">
         <v>-5.89</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>18.82</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44125</v>
+        <v>44126</v>
       </c>
       <c r="H36" t="n">
-        <v>603.8</v>
+        <v>589.75</v>
       </c>
       <c r="I36" t="n">
         <v>597.8232342909512</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K36" t="n">
-        <v>4.64</v>
+        <v>2.2</v>
       </c>
       <c r="L36" t="n">
         <v>11.11</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>23.04</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44175</v>
+        <v>44176</v>
       </c>
       <c r="H37" t="n">
-        <v>618.15</v>
+        <v>657.05</v>
       </c>
       <c r="I37" t="n">
         <v>631.8534221091209</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.82</v>
+        <v>-11.41</v>
       </c>
       <c r="L37" t="n">
-        <v>5.82</v>
+        <v>12.32</v>
       </c>
       <c r="M37" t="n">
         <v>2.43</v>
       </c>
       <c r="N37" t="n">
-        <v>4.93</v>
+        <v>6.29</v>
       </c>
       <c r="O37" t="n">
         <v>-2.33</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>12.5</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H38" t="n">
-        <v>2032.15</v>
+        <v>1954.55</v>
       </c>
       <c r="I38" t="n">
         <v>1959.177561190433</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K38" t="n">
-        <v>209.28</v>
+        <v>197.47</v>
       </c>
       <c r="L38" t="n">
         <v>5.94</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>236</v>
+        <v>237</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>13</v>
+      </c>
+      <c r="U38" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>14.21</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44540</v>
+        <v>44543</v>
       </c>
       <c r="H39" t="n">
-        <v>2168.8</v>
+        <v>2206.5</v>
       </c>
       <c r="I39" t="n">
         <v>2201.945776100556</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K39" t="n">
-        <v>-10.96</v>
+        <v>-12.89</v>
       </c>
       <c r="L39" t="n">
-        <v>13.45</v>
+        <v>16.4</v>
       </c>
       <c r="M39" t="n">
         <v>1</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>9.76</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44575</v>
+        <v>44578</v>
       </c>
       <c r="H40" t="n">
-        <v>2222.8</v>
+        <v>2188.9</v>
       </c>
       <c r="I40" t="n">
         <v>2212.430513096087</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K40" t="n">
-        <v>0.74</v>
+        <v>-0.8</v>
       </c>
       <c r="L40" t="n">
         <v>1.99</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44631</v>
+        <v>44634</v>
       </c>
       <c r="H41" t="n">
-        <v>2179.3</v>
+        <v>2237.55</v>
       </c>
       <c r="I41" t="n">
         <v>2200.094709348487</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K41" t="n">
-        <v>0.44</v>
+        <v>-2.22</v>
       </c>
       <c r="L41" t="n">
         <v>3.75</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>12.77</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44662</v>
+        <v>44663</v>
       </c>
       <c r="H42" t="n">
-        <v>2257.7</v>
+        <v>2191.4</v>
       </c>
       <c r="I42" t="n">
         <v>2235.416749833847</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K42" t="n">
-        <v>0.9</v>
+        <v>-2.06</v>
       </c>
       <c r="L42" t="n">
         <v>4.11</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>12.15</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44763</v>
+        <v>44764</v>
       </c>
       <c r="H43" t="n">
-        <v>1781.5</v>
+        <v>1816.4</v>
       </c>
       <c r="I43" t="n">
         <v>1803.215175644984</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K43" t="n">
-        <v>18.7</v>
+        <v>17.11</v>
       </c>
       <c r="L43" t="n">
         <v>3.7</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>11.75</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44799</v>
+        <v>44802</v>
       </c>
       <c r="H44" t="n">
-        <v>1762.8</v>
+        <v>1713.4</v>
       </c>
       <c r="I44" t="n">
         <v>1718.789147017185</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.95</v>
+        <v>-5.67</v>
       </c>
       <c r="L44" t="n">
         <v>9.4</v>
       </c>
       <c r="M44" t="n">
-        <v>2.52</v>
+        <v>4.13</v>
       </c>
       <c r="N44" t="n">
         <v>7.56</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>11.24</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44838</v>
+        <v>44840</v>
       </c>
       <c r="H45" t="n">
-        <v>1649.45</v>
+        <v>1776.4</v>
       </c>
       <c r="I45" t="n">
         <v>1741.487321847311</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K45" t="n">
-        <v>3.73</v>
+        <v>-3.68</v>
       </c>
       <c r="L45" t="n">
-        <v>3.25</v>
+        <v>4.19</v>
       </c>
       <c r="M45" t="n">
-        <v>1.68</v>
+        <v>2.22</v>
       </c>
       <c r="N45" t="n">
-        <v>3.48</v>
+        <v>7.7</v>
       </c>
       <c r="O45" t="n">
         <v>-2.8</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>13.25</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44903</v>
+        <v>44904</v>
       </c>
       <c r="H46" t="n">
-        <v>2051.1</v>
+        <v>1977.8</v>
       </c>
       <c r="I46" t="n">
         <v>1991.075424702736</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K46" t="n">
-        <v>15.46</v>
+        <v>11.34</v>
       </c>
       <c r="L46" t="n">
         <v>5.91</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>12.09</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44944</v>
+        <v>44945</v>
       </c>
       <c r="H47" t="n">
-        <v>1979.8</v>
+        <v>2129.1</v>
       </c>
       <c r="I47" t="n">
         <v>2082.683558651727</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.1</v>
+        <v>-7.65</v>
       </c>
       <c r="L47" t="n">
-        <v>6.81</v>
+        <v>8.15</v>
       </c>
       <c r="M47" t="n">
         <v>1.76</v>
       </c>
       <c r="N47" t="n">
-        <v>4.06</v>
+        <v>7.54</v>
       </c>
       <c r="O47" t="n">
         <v>-3.57</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>13.4</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44998</v>
+        <v>44999</v>
       </c>
       <c r="H48" t="n">
-        <v>2311</v>
+        <v>2266.55</v>
       </c>
       <c r="I48" t="n">
         <v>2303.529220551266</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K48" t="n">
-        <v>8.539999999999999</v>
+        <v>6.46</v>
       </c>
       <c r="L48" t="n">
         <v>7.94</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>9.35</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45042</v>
+        <v>45043</v>
       </c>
       <c r="H49" t="n">
-        <v>2236.1</v>
+        <v>2291.6</v>
       </c>
       <c r="I49" t="n">
         <v>2279.75987556167</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K49" t="n">
-        <v>1.34</v>
+        <v>-1.11</v>
       </c>
       <c r="L49" t="n">
         <v>2.8</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>11.17</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45085</v>
+        <v>45086</v>
       </c>
       <c r="H50" t="n">
-        <v>2463.1</v>
+        <v>2443.4</v>
       </c>
       <c r="I50" t="n">
         <v>2448.519175506996</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K50" t="n">
-        <v>7.48</v>
+        <v>6.62</v>
       </c>
       <c r="L50" t="n">
         <v>3.02</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>7.61</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45125</v>
+        <v>45126</v>
       </c>
       <c r="H51" t="n">
-        <v>2491.7</v>
+        <v>2569.35</v>
       </c>
       <c r="I51" t="n">
         <v>2504.544162787882</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.98</v>
+        <v>-5.15</v>
       </c>
       <c r="L51" t="n">
-        <v>4.14</v>
+        <v>5.37</v>
       </c>
       <c r="M51" t="n">
         <v>1.23</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>9.82</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45132</v>
+        <v>45133</v>
       </c>
       <c r="H52" t="n">
-        <v>2341.5</v>
+        <v>2332.1</v>
       </c>
       <c r="I52" t="n">
         <v>2338.236358183845</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K52" t="n">
-        <v>-8.869999999999999</v>
+        <v>-9.23</v>
       </c>
       <c r="L52" t="n">
-        <v>9.33</v>
+        <v>9.65</v>
       </c>
       <c r="M52" t="n">
         <v>3.05</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>9.56</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45161</v>
+        <v>45162</v>
       </c>
       <c r="H53" t="n">
-        <v>2502.55</v>
+        <v>2560</v>
       </c>
       <c r="I53" t="n">
         <v>2521.781857115057</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K53" t="n">
-        <v>-7.31</v>
+        <v>-9.77</v>
       </c>
       <c r="L53" t="n">
-        <v>8.83</v>
+        <v>10.39</v>
       </c>
       <c r="M53" t="n">
         <v>0.8100000000000001</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>7.63</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
       <c r="H54" t="n">
-        <v>4117.3</v>
+        <v>4105.4</v>
       </c>
       <c r="I54" t="n">
         <v>4105.437620482316</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K54" t="n">
-        <v>60.83</v>
+        <v>60.37</v>
       </c>
       <c r="L54" t="n">
         <v>2.13</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>8</v>
+      </c>
+      <c r="U54" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>7.85</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45436</v>
+        <v>45439</v>
       </c>
       <c r="H55" t="n">
-        <v>3555.2</v>
+        <v>3736.7</v>
       </c>
       <c r="I55" t="n">
         <v>3651.220917880782</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="K55" t="n">
-        <v>13.4</v>
+        <v>8.98</v>
       </c>
       <c r="L55" t="n">
         <v>2.97</v>
@@ -3576,7 +4235,7 @@
         <v>2.14</v>
       </c>
       <c r="N55" t="n">
-        <v>2.53</v>
+        <v>5.11</v>
       </c>
       <c r="O55" t="n">
         <v>-0.29</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>9.43</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45442</v>
+        <v>45443</v>
       </c>
       <c r="H56" t="n">
-        <v>3517.05</v>
+        <v>3410.5</v>
       </c>
       <c r="I56" t="n">
         <v>3438.640174276971</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K56" t="n">
-        <v>-5.88</v>
+        <v>-8.73</v>
       </c>
       <c r="L56" t="n">
-        <v>6.31</v>
+        <v>9.01</v>
       </c>
       <c r="M56" t="n">
         <v>0.27</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>11.15</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45449</v>
+        <v>45450</v>
       </c>
       <c r="H57" t="n">
-        <v>3694.35</v>
+        <v>3850.25</v>
       </c>
       <c r="I57" t="n">
         <v>3704.863532491191</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K57" t="n">
-        <v>-8.32</v>
+        <v>-12.89</v>
       </c>
       <c r="L57" t="n">
-        <v>8.92</v>
+        <v>13.57</v>
       </c>
       <c r="M57" t="n">
         <v>2.93</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>12.14</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H58" t="n">
-        <v>6319.65</v>
+        <v>6003.4</v>
       </c>
       <c r="I58" t="n">
         <v>6173.271106099734</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K58" t="n">
-        <v>64.14</v>
+        <v>55.92</v>
       </c>
       <c r="L58" t="n">
         <v>4.47</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>149</v>
+        <v>150</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>8</v>
+      </c>
+      <c r="U58" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>12.79</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45771</v>
+        <v>45772</v>
       </c>
       <c r="H59" t="n">
-        <v>5156.5</v>
+        <v>5273.5</v>
       </c>
       <c r="I59" t="n">
         <v>5255.430058770405</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K59" t="n">
-        <v>14.11</v>
+        <v>12.16</v>
       </c>
       <c r="L59" t="n">
         <v>8.289999999999999</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>5</v>
+      </c>
+      <c r="U59" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>14.87</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45848</v>
+        <v>45849</v>
       </c>
       <c r="H60" t="n">
-        <v>5680.5</v>
+        <v>5578.5</v>
       </c>
       <c r="I60" t="n">
         <v>5679.163090549599</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K60" t="n">
-        <v>7.72</v>
+        <v>5.78</v>
       </c>
       <c r="L60" t="n">
         <v>2.57</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.89</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="H61" t="n">
-        <v>5363.5</v>
+        <v>5490.5</v>
       </c>
       <c r="I61" t="n">
         <v>5481.066660317762</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K61" t="n">
-        <v>3.85</v>
+        <v>1.58</v>
       </c>
       <c r="L61" t="n">
         <v>4.85</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>8.77</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="H62" t="n">
-        <v>5191.5</v>
+        <v>5102.5</v>
       </c>
       <c r="I62" t="n">
         <v>5142.662710224068</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K62" t="n">
-        <v>-5.45</v>
+        <v>-7.07</v>
       </c>
       <c r="L62" t="n">
-        <v>6.53</v>
+        <v>7.49</v>
       </c>
       <c r="M62" t="n">
         <v>2.83</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>10.11</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="H63" t="n">
-        <v>5263.6</v>
+        <v>5345.3</v>
       </c>
       <c r="I63" t="n">
         <v>5300.251650446677</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.16</v>
+        <v>-4.76</v>
       </c>
       <c r="L63" t="n">
-        <v>4.56</v>
+        <v>4.95</v>
       </c>
       <c r="M63" t="n">
         <v>0.77</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.65</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="H64" t="n">
-        <v>6302</v>
+        <v>6033.5</v>
       </c>
       <c r="I64" t="n">
         <v>6119.082895800588</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K64" t="n">
-        <v>17.9</v>
+        <v>12.87</v>
       </c>
       <c r="L64" t="n">
         <v>2.68</v>
@@ -4089,7 +4856,7 @@
         <v>1.63</v>
       </c>
       <c r="N64" t="n">
-        <v>2.66</v>
+        <v>4.26</v>
       </c>
       <c r="O64" t="n">
         <v>1.55</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>10.4</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="H65" t="n">
-        <v>5049.1</v>
+        <v>5227.7</v>
       </c>
       <c r="I65" t="n">
         <v>5217.533820554735</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K65" t="n">
-        <v>16.32</v>
+        <v>13.36</v>
       </c>
       <c r="L65" t="n">
         <v>9.369999999999999</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>5</v>
+      </c>
+      <c r="U65" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>13.31</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="H66" t="n">
-        <v>5065.2</v>
+        <v>4747.3</v>
       </c>
       <c r="I66" t="n">
         <v>4992.425553616752</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K66" t="n">
-        <v>-3.11</v>
+        <v>-9.19</v>
       </c>
       <c r="L66" t="n">
-        <v>5.05</v>
+        <v>9.44</v>
       </c>
       <c r="M66" t="n">
         <v>2.1</v>
       </c>
       <c r="N66" t="n">
-        <v>4.81</v>
+        <v>6.28</v>
       </c>
       <c r="O66" t="n">
         <v>3.54</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>15.82</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="H67" t="n">
-        <v>5194.3</v>
+        <v>5402</v>
       </c>
       <c r="I67" t="n">
         <v>5210.114798518836</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K67" t="n">
-        <v>-9.42</v>
+        <v>-13.79</v>
       </c>
       <c r="L67" t="n">
-        <v>11.18</v>
+        <v>15.81</v>
       </c>
       <c r="M67" t="n">
         <v>1.32</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>10.2</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="H68" t="n">
-        <v>5018</v>
+        <v>4928</v>
       </c>
       <c r="I68" t="n">
         <v>4990.457302661042</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K68" t="n">
-        <v>-7.11</v>
+        <v>-8.77</v>
       </c>
       <c r="L68" t="n">
         <v>9.09</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,25 +5180,25 @@
         <v>13.03</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="H69" t="n">
-        <v>4829.9</v>
+        <v>5053.9</v>
       </c>
       <c r="I69" t="n">
         <v>4886.269550727311</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K69" t="n">
-        <v>1.99</v>
+        <v>-2.55</v>
       </c>
       <c r="L69" t="n">
         <v>3.59</v>
       </c>
       <c r="M69" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="N69" t="n">
         <v>5.78</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>12.33</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="H70" t="n">
-        <v>5366</v>
+        <v>5240</v>
       </c>
       <c r="I70" t="n">
         <v>5358.381844258221</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K70" t="n">
-        <v>6.18</v>
+        <v>3.68</v>
       </c>
       <c r="L70" t="n">
         <v>2.99</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="H71" t="n">
-        <v>5468</v>
+        <v>5770</v>
       </c>
       <c r="I71" t="n">
         <v>5699.247332465095</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K71" t="n">
-        <v>-4.35</v>
+        <v>-10.11</v>
       </c>
       <c r="L71" t="n">
-        <v>7.42</v>
+        <v>10.48</v>
       </c>
       <c r="M71" t="n">
         <v>1.51</v>
       </c>
       <c r="N71" t="n">
-        <v>3.04</v>
+        <v>5.52</v>
       </c>
       <c r="O71" t="n">
         <v>-2.35</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4548,6 +5411,14 @@
       <c r="Q72" t="n">
         <v>13</v>
       </c>
+      <c r="R72" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9506,7 +10377,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.8</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="6">
@@ -9516,7 +10387,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="7">
@@ -9526,7 +10397,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8">
@@ -9536,7 +10407,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -9546,7 +10417,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="10">
@@ -9556,7 +10427,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>116.1</v>
+        <v>117.1</v>
       </c>
     </row>
     <row r="11">
@@ -9566,7 +10437,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -9576,7 +10447,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -9586,7 +10457,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="14">
@@ -9596,7 +10467,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.75</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="15">
@@ -9606,7 +10477,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13.61</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="16">
@@ -9616,7 +10487,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.89</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="17">
@@ -9626,7 +10497,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>209.28</v>
+        <v>197.47</v>
       </c>
     </row>
     <row r="18">
@@ -9636,7 +10507,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>57.1</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="19">
@@ -9646,7 +10517,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.06</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="20">
@@ -9656,7 +10527,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.47</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="21">
@@ -9666,7 +10537,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.04</v>
+        <v>23.98</v>
       </c>
     </row>
     <row r="22">
@@ -9676,7 +10547,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
@@ -9686,7 +10557,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -9696,7 +10567,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="25">
@@ -9706,7 +10577,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.97</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="26">
@@ -9716,7 +10587,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.3</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="27">
@@ -9726,7 +10597,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.64</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="28">
@@ -9736,7 +10607,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29">
